--- a/data/evals/calibration/judge_calibration_v1b.xlsx
+++ b/data/evals/calibration/judge_calibration_v1b.xlsx
@@ -1603,16 +1603,8 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L15" s="5" t="inlineStr">
-        <is>
-          <t>owner rubric: strict reading, 2026-10-11</t>
-        </is>
-      </c>
+      <c r="K15" s="5" t="inlineStr"/>
+      <c r="L15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1677,16 +1669,8 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L16" s="5" t="inlineStr">
-        <is>
-          <t>owner rubric: strict reading, 2026-10-11</t>
-        </is>
-      </c>
+      <c r="K16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -1883,16 +1867,8 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L19" s="5" t="inlineStr">
-        <is>
-          <t>owner rubric: strict reading, 2026-10-11</t>
-        </is>
-      </c>
+      <c r="K19" s="5" t="inlineStr"/>
+      <c r="L19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
